--- a/templates/xlsx/content-positioning.xlsx
+++ b/templates/xlsx/content-positioning.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Content Positioning Board" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="About" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>

--- a/templates/xlsx/content-positioning.xlsx
+++ b/templates/xlsx/content-positioning.xlsx
@@ -478,7 +478,7 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>A · Stop (0-3s)</t>
+          <t>A · Stop (0-3s; hold through 6s)</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
